--- a/smash_ultimate_moveset_mods.xlsx
+++ b/smash_ultimate_moveset_mods.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moveset Mods'!$A$1:$K$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moveset Mods'!$A$1:$L$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -166,10 +166,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -537,23 +537,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>original_char</t>
@@ -606,7 +607,12 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>sugg1_confidence</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>sugg2_confidence</t>
         </is>
       </c>
     </row>
@@ -649,7 +655,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr"/>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -704,7 +715,12 @@
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>sugg2 link = Discord server</t>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
         </is>
       </c>
     </row>
@@ -736,6 +752,7 @@
         </is>
       </c>
       <c r="K4" s="14" t="inlineStr"/>
+      <c r="L4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -776,7 +793,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -806,6 +828,7 @@
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -835,6 +858,7 @@
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr"/>
+      <c r="L7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -864,6 +888,7 @@
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -893,35 +918,53 @@
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Pikachu</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr"/>
-      <c r="F10" s="13" t="inlineStr"/>
-      <c r="G10" s="13" t="inlineStr"/>
-      <c r="H10" s="13" t="inlineStr"/>
-      <c r="I10" s="13" t="inlineStr"/>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>no custom moveset exists</t>
-        </is>
-      </c>
-      <c r="K10" s="14" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Raichu</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/474333</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>single option available</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>slotted ecosystem; slot range not published</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -951,6 +994,7 @@
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr"/>
+      <c r="L11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1003,7 +1047,16 @@
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K12" s="10" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1056,7 +1109,16 @@
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1111,7 +1173,12 @@
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>joke mod</t>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
         </is>
       </c>
     </row>
@@ -1156,9 +1223,10 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>sugg1 link = UMC entry (no public mirror)</t>
-        </is>
-      </c>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -1188,6 +1256,7 @@
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1228,7 +1297,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -1258,6 +1332,7 @@
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr"/>
+      <c r="L18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -1287,6 +1362,7 @@
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr"/>
+      <c r="L19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1327,7 +1403,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1380,7 +1461,16 @@
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1421,7 +1511,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1462,7 +1557,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -1517,7 +1617,12 @@
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>sugg2 link = UMC entry (no public mirror)</t>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
         </is>
       </c>
     </row>
@@ -1549,6 +1654,7 @@
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr"/>
+      <c r="L25" s="14" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -1578,6 +1684,7 @@
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr"/>
+      <c r="L26" s="14" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -1630,7 +1737,16 @@
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -1683,7 +1799,16 @@
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K28" s="10" t="inlineStr"/>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -1713,6 +1838,7 @@
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr"/>
+      <c r="L29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1753,7 +1879,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -1783,6 +1914,7 @@
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr"/>
+      <c r="L31" s="14" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1825,9 +1957,10 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>sugg1 link = Discord server</t>
-        </is>
-      </c>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -1857,47 +1990,69 @@
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr"/>
+      <c r="L33" s="14" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Dark Pit</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Krystal</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/514829</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Decidueye</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/513821</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>64-71</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>single option available</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr"/>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>compatible stack; confirm slots on install</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>slotted ecosystem; slot range not published</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -1927,6 +2082,7 @@
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr"/>
+      <c r="L35" s="14" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -1956,6 +2112,7 @@
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr"/>
+      <c r="L36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -1985,6 +2142,7 @@
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr"/>
+      <c r="L37" s="14" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -2037,7 +2195,16 @@
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K38" s="10" t="inlineStr"/>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -2067,6 +2234,7 @@
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr"/>
+      <c r="L39" s="14" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -2096,6 +2264,7 @@
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr"/>
+      <c r="L40" s="14" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2136,7 +2305,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -2189,7 +2363,16 @@
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr"/>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -2219,6 +2402,7 @@
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr"/>
+      <c r="L43" s="14" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2259,36 +2443,58 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Lucario</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="inlineStr"/>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr"/>
-      <c r="F45" s="13" t="inlineStr"/>
-      <c r="G45" s="13" t="inlineStr"/>
-      <c r="H45" s="13" t="inlineStr"/>
-      <c r="I45" s="13" t="inlineStr"/>
-      <c r="J45" s="14" t="inlineStr">
-        <is>
-          <t>no custom moveset exists</t>
-        </is>
-      </c>
-      <c r="K45" s="14" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Vegeta</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/469216</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>single option available</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>slotted ecosystem; slot range not published</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -2318,6 +2524,7 @@
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr"/>
+      <c r="L46" s="14" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -2347,35 +2554,53 @@
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr"/>
+      <c r="L47" s="14" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="inlineStr"/>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr"/>
-      <c r="F48" s="13" t="inlineStr"/>
-      <c r="G48" s="13" t="inlineStr"/>
-      <c r="H48" s="13" t="inlineStr"/>
-      <c r="I48" s="13" t="inlineStr"/>
-      <c r="J48" s="14" t="inlineStr">
-        <is>
-          <t>no custom moveset exists</t>
-        </is>
-      </c>
-      <c r="K48" s="14" t="inlineStr"/>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Zeraora</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/524527</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>single option available</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>slotted ecosystem; slot range not published</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2416,48 +2641,74 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>Mega Man</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/605585</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Colette</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/561040</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>95-102</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>single option available</t>
-        </is>
-      </c>
-      <c r="K50" s="6" t="inlineStr"/>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>compatible stack; confirm slots on install</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>slotted ecosystem; slot range not published</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -2487,6 +2738,7 @@
         </is>
       </c>
       <c r="K51" s="14" t="inlineStr"/>
+      <c r="L51" s="14" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -2516,35 +2768,53 @@
         </is>
       </c>
       <c r="K52" s="14" t="inlineStr"/>
+      <c r="L52" s="14" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Little Mac</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="C53" s="13" t="inlineStr"/>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr"/>
-      <c r="F53" s="13" t="inlineStr"/>
-      <c r="G53" s="13" t="inlineStr"/>
-      <c r="H53" s="13" t="inlineStr"/>
-      <c r="I53" s="13" t="inlineStr"/>
-      <c r="J53" s="14" t="inlineStr">
-        <is>
-          <t>no custom moveset exists</t>
-        </is>
-      </c>
-      <c r="K53" s="14" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Naruto Uzumaki</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/478432</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr"/>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>single option available</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>slotted ecosystem; slot range not published</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2585,7 +2855,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K54" s="6" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -2615,6 +2890,7 @@
         </is>
       </c>
       <c r="K55" s="14" t="inlineStr"/>
+      <c r="L55" s="14" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -2644,6 +2920,7 @@
         </is>
       </c>
       <c r="K56" s="14" t="inlineStr"/>
+      <c r="L56" s="14" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -2673,6 +2950,7 @@
         </is>
       </c>
       <c r="K57" s="14" t="inlineStr"/>
+      <c r="L57" s="14" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -2725,7 +3003,16 @@
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K58" s="10" t="inlineStr"/>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2766,36 +3053,58 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Robin</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="C60" s="13" t="inlineStr"/>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E60" s="13" t="inlineStr"/>
-      <c r="F60" s="13" t="inlineStr"/>
-      <c r="G60" s="13" t="inlineStr"/>
-      <c r="H60" s="13" t="inlineStr"/>
-      <c r="I60" s="13" t="inlineStr"/>
-      <c r="J60" s="14" t="inlineStr">
-        <is>
-          <t>no custom moveset exists</t>
-        </is>
-      </c>
-      <c r="K60" s="14" t="inlineStr"/>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Mona</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/533215</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>single option available</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>slotted ecosystem; slot range not published</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -2825,6 +3134,7 @@
         </is>
       </c>
       <c r="K61" s="14" t="inlineStr"/>
+      <c r="L61" s="14" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -2854,6 +3164,7 @@
         </is>
       </c>
       <c r="K62" s="14" t="inlineStr"/>
+      <c r="L62" s="14" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -2883,6 +3194,7 @@
         </is>
       </c>
       <c r="K63" s="14" t="inlineStr"/>
+      <c r="L63" s="14" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
@@ -2912,6 +3224,7 @@
         </is>
       </c>
       <c r="K64" s="14" t="inlineStr"/>
+      <c r="L64" s="14" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2952,7 +3265,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
@@ -2982,6 +3300,7 @@
         </is>
       </c>
       <c r="K66" s="14" t="inlineStr"/>
+      <c r="L66" s="14" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3024,9 +3343,10 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>sugg1 link = UMC entry (no public mirror)</t>
-        </is>
-      </c>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -3056,6 +3376,7 @@
         </is>
       </c>
       <c r="K68" s="14" t="inlineStr"/>
+      <c r="L68" s="14" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
@@ -3085,6 +3406,7 @@
         </is>
       </c>
       <c r="K69" s="14" t="inlineStr"/>
+      <c r="L69" s="14" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
@@ -3114,6 +3436,7 @@
         </is>
       </c>
       <c r="K70" s="14" t="inlineStr"/>
+      <c r="L70" s="14" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -3143,6 +3466,7 @@
         </is>
       </c>
       <c r="K71" s="14" t="inlineStr"/>
+      <c r="L71" s="14" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3183,7 +3507,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K72" s="6" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -3213,6 +3542,7 @@
         </is>
       </c>
       <c r="K73" s="14" t="inlineStr"/>
+      <c r="L73" s="14" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -3242,6 +3572,7 @@
         </is>
       </c>
       <c r="K74" s="14" t="inlineStr"/>
+      <c r="L74" s="14" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -3271,6 +3602,7 @@
         </is>
       </c>
       <c r="K75" s="14" t="inlineStr"/>
+      <c r="L75" s="14" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
@@ -3300,6 +3632,7 @@
         </is>
       </c>
       <c r="K76" s="14" t="inlineStr"/>
+      <c r="L76" s="14" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
@@ -3329,6 +3662,7 @@
         </is>
       </c>
       <c r="K77" s="14" t="inlineStr"/>
+      <c r="L77" s="14" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3369,7 +3703,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K78" s="6" t="inlineStr"/>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3410,7 +3749,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K79" s="6" t="inlineStr"/>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -3463,7 +3807,16 @@
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K80" s="10" t="inlineStr"/>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
@@ -3493,6 +3846,7 @@
         </is>
       </c>
       <c r="K81" s="14" t="inlineStr"/>
+      <c r="L81" s="14" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
@@ -3522,6 +3876,7 @@
         </is>
       </c>
       <c r="K82" s="14" t="inlineStr"/>
+      <c r="L82" s="14" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
@@ -3551,6 +3906,7 @@
         </is>
       </c>
       <c r="K83" s="14" t="inlineStr"/>
+      <c r="L83" s="14" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3591,7 +3947,12 @@
           <t>single option available</t>
         </is>
       </c>
-      <c r="K84" s="6" t="inlineStr"/>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks checked)</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
@@ -3621,6 +3982,7 @@
         </is>
       </c>
       <c r="K85" s="14" t="inlineStr"/>
+      <c r="L85" s="14" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
@@ -3650,6 +4012,7 @@
         </is>
       </c>
       <c r="K86" s="14" t="inlineStr"/>
+      <c r="L86" s="14" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
@@ -3679,56 +4042,64 @@
         </is>
       </c>
       <c r="K87" s="14" t="inlineStr"/>
+      <c r="L87" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K87"/>
+  <autoFilter ref="A1:L87"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3740,12 +4111,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3774,128 +4144,88 @@
           <t>Download</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>Used by</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>The CSK Collection</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/499008</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>89/91</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>NRO Hook</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>https://github.com/ultimate-research/nro-hook-plugin/releases</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>89/91</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Smashline 2</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>https://github.com/HDR-Development/smashline</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>89/91</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>ARCropolis</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>https://github.com/Raytwo/ARCropolis</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>88/91</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Skyline</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>https://github.com/skyline-dev/skyline</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>88/91</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>paramconfig</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>https://github.com/CSharpM7/lib_paramconfig</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>88/91</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>One Slot Effects</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/549058</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>78/91</t>
         </is>
       </c>
     </row>
@@ -3903,119 +4233,162 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
+          <t>CONFIDENCE LEVELS (see sugg1_confidence / sugg2_confidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>'verified (slots+hooks checked)' - tracked in the Ultimate Moveset Compatibility database. Costume slot range and</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    hooked memory offsets are published, so conflicts were checked programmatically. Highest confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>'slotted ecosystem; slot range not published' - GameBanana mod confirmed to use the CSK slotting method / Smashline 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (same plugin stack), but its slot range is not published, so overlap could not be auto-verified. Confirm on install.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>WHY THESE MODS ARE INTERCOMPATIBLE</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>1. Every listed moveset is SLOTTED: it occupies a specific costume-slot range (columns sugg1_slots / sugg2_slots)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    instead of replacing the fighter globally. Two movesets on one fighter coexist when their slot ranges differ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>2. All are built on the same Smashline 2 + ARCropolis stack above, so they share one plugin set instead of conflicting ones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>3. Each pair below was checked programmatically for (a) slot-range overlap, (b) shared hooked memory offsets,</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    and (c) both using a global 'opff' (once-per-frame) hook. Only conflict-free pairs were selected.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>4. AVOID non-slotted / older movesets (typical pre-Smashline-2 GameBanana uploads): they overwrite the entire fighter and</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    break every other mod on that character. That constraint is why this list is limited to the slotted ecosystem.</t>
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>1. Every listed moveset is SLOTTED: it occupies specific costume slots rather than replacing the fighter globally,</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>5. If you ever hit a slot overlap, ranges can be reassigned with a reslotter tool.</t>
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    so several can coexist. Two movesets on one fighter are fine as long as their slot ranges differ.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>6. Movesets are not Wi-Fi safe - use them offline / in local play only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>2. All share the Smashline 2 + ARCropolis + CSK stack above - one plugin set, not competing ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>3. Tier-A pairs were checked for slot-range overlap, shared hooked memory offsets, and concurrent global 'opff' hooks.</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>SCOPE / COVERAGE</t>
+          <t>4. EXCLUDED: non-slotted movesets, which overwrite the whole fighter and break every other mod on it. The most popular</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Only 34 of 86 fighters have a released slotted custom moveset; 12 have two. Remaining fighters have none in existence.</t>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    moveset in the game (Shadow the Hedgehog, 465 likes) is excluded for exactly this reason - it states no slotting.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>Roster uses the 86 in-game fighter slots (Pokemon Trainer = 1 entry, Pyra / Mythra = 1 entry).</t>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>5. Also excluded: reworks of a vanilla fighter (Sonic Re-Imagined, Dread Samus, Swole Luigi). They change the original</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>'NONE AVAILABLE' means no such mod exists - not that it was omitted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    character rather than replacing them, so they do not answer 'which mod character replaces X'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>6. Slot ranges can be reassigned with a reslotter tool if you hit an overlap.</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>https://lilylavender.github.io/UltimateMovesetCompatibility/</t>
-        </is>
-      </c>
-    </row>
+          <t>7. Movesets are NOT Wi-Fi safe - offline / local play only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>COVERAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>39 of 86 fighters have at least one custom moveset; 14 have two. 47 have none in existence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>'NONE AVAILABLE' means no such mod has been made - not that it was omitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Roster = 86 in-game fighter slots (Pokemon Trainer = 1 entry, Pyra / Mythra = 1 entry).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>https://lilylavender.github.io/UltimateMovesetCompatibility/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/cats/3325</t>
         </is>
@@ -4030,8 +4403,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4076,7 +4449,7 @@
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Fighters with at least 1 custom moveset</t>
+          <t>Fighters with at least 1 moveset</t>
         </is>
       </c>
       <c r="B3" s="21">
@@ -4098,7 +4471,7 @@
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>Fighters with NO custom moveset</t>
+          <t>Fighters with NO moveset</t>
         </is>
       </c>
       <c r="B5" s="21">

--- a/smash_ultimate_moveset_mods.xlsx
+++ b/smash_ultimate_moveset_mods.xlsx
@@ -7,12 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Moveset Mods" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Setup &amp; Compatibility" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mod Roster" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="By Original Char" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Setup &amp; Compatibility" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Moveset Mods'!$A$1:$L$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mod Roster'!$A$1:$I$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'By Original Char'!$A$1:$L$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -81,12 +83,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -133,9 +135,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,6 +152,9 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -166,10 +168,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -537,21 +538,3280 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mod_char</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>replaces_host</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>slots</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>likes</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>joke</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>A-Bomb</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Mugen</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Jigglypuff</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>32-33</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/665659</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>joke mod</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Akaza</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Demon Slayer</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Captain Falcon</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>40-47</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/659845</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Alucard</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Castlevania</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Richter</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/457661</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Armstrong</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Metal Gear</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Ganondorf</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>8-15</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/485221</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Bandana Dee</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Kirby</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Sephiroth</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/580288</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Black Knight</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Fire Emblem</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Ike</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/589645</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Blaziken</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Pokémon</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Captain Falcon</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/540179</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Blood Falcon</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>F-Zero</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Captain Falcon</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>24-31</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/496231</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Bluster Kong</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Donkey Kong</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Donkey Kong</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>64-71</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://discord.gg/PdTDUgNYaY </t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Open Beta</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Bomb</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Angry Birds</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Jigglypuff</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>24-31</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/665651</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>joke mod</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Bomberman</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Bomberman</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>PAC-Man</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/38894</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Chaos</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Greninja</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>64-71</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/641872</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Colette</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Tales of Symphonia</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Mega Man</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/561040</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Cuphead</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Cuphead</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Banjo &amp; Kazooie</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>32-39</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/633920</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Dark Meta Knight</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Kirby</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Meta Knight</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>72-79</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>https://discord.gg/mXGbCkakR</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Open Beta</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Decidueye</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Pokemon</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Dark Pit</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/513821</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Diluc</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Genshin Impact</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Ike</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/507238</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Ermac</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Mortal Kombat</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Mewtwo</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/487662</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Funky Kong</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Donkey Kong</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Donkey Kong</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/549673</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Gengar &amp; Charmeleon</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Pokemon</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Mewtwo</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/525595</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Geralt</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>The Witcher</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Ike</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>64-71</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/637095</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Open Beta</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Gogeta</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Dragon Ball</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Terry</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>103-110</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/493356</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Goku</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Dragon Ball</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Marth</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>80-87</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>https://lilylavender.github.io/UltimateMovesetCompatibility/moveset/95</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Open Beta</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Goomba</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Mario</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Pichu</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/639737</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Herobrine</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Minecraft</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Mewtwo</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>32-39</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/559266</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Pending Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Hilda</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Fire Emblem</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Ike</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>128-135</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/361574</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Ichiban</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Yakuza</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Chrom</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>95-103</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/660071</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Iron Man</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Avengers</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Mario</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>48-55</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/660142</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Jiren</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Dragon Ball</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Ganondorf</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>80-87</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/544880</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Kale</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Dragon Ball</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Ganondorf</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/484550</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Kamek</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Yoshi</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Ness</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>64-71</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/510382</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>King Leno</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Leon (Custom)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Bowser</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>24-31</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/674935</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Knuckles</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/606587</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Krystal</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Star Fox</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Dark Pit</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>64-71</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/514829</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Magolor</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Kirby</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Jigglypuff</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>96-111</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/630469</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Masked Man</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>EarthBound</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/489945</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Mecha Sonic</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Samus</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>80-87</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/495584</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Megumin</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Konosuba</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>64-71</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/660152</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Meiling</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Touhou</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Terry</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/583913</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Mona</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>WarioWare</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Robin</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/533215</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Monster Hunter</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Monster Hunter</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Ike</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>104-111</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/678083</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Naruto Uzumaki</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Naruto</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Little Mac</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/478432</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Ninten</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>EarthBound</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Ness</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/468526</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Pawn</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Mario</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>41-48</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/664660</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Peppy</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Star Fox</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Falco</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/38894</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Phoenix Wright</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Ace Attorney</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Captain Falcon</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>112-119</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/606758</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Phosphora</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Kid Icarus</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Zelda</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>128-135</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/471696</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Potemkin</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Guilty Gear</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Corrin</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>128-144</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>https://lilylavender.github.io/UltimateMovesetCompatibility/moveset/45</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Open Beta</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Raichu</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Pokemon</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Pikachu</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/474333</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Rayman</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Rayman</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Olimar</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/38894</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Sailor Moon</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Sailor Moon</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Palutena</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>128-135</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/390285</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Sandbag</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Super Smash Bros.</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Mario</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>64-71</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/481498</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Sans</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Undertale</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Palutena</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/549674</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Sasuke Uchiha</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Naruto</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Marth</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/526228</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Shadow Mewtwo</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Pokémon</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Mewtwo</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>24-31</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/583298</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Mewtwo</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>128-135</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/470041</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Springtrap</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Five Nights at Freddy's</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Ganondorf</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>16-23</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/675046</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Open Beta</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Tails</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>64-71</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/635053</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Tetrimino</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Tetris</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Marth</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>20-27</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/626305</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>The Crash</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Spin</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Mario</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>8-15</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/665674</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>joke mod</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>THE EGGMAN</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Eggman</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>24-31</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/665617</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>joke mod</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Toad</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Mario</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Villager</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/38894</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Ultron</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Avengers</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Ganondorf</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>64-71</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/681333</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Uravity</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>My Hero Academia</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Peach</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>100-107</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>https://lilylavender.github.io/UltimateMovesetCompatibility/moveset/96</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Open Beta</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Vegeta</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Dragon Ball</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Ken</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>95-102</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/699357</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Vegeta</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Dragon Ball</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Lucario</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/469216</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Vegito</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Dragon Ball</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Marth</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/472557</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Waluigi</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Wario</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Terry</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>120-127</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/443150</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Weiss</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>RWBY</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Marth</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>128-135</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/415034</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Mega Man X</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Mega Man</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>95-102</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/605585</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Z Broly</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Dragon Ball</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Ganondorf</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>40-47</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/630616</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>verified (slots+hooks published)</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Zeraora</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Pokemon</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>not published</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/524527</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>slotted (CSK/Smashline 2); slots not published</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I73"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId72"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -617,108 +3877,108 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Mario</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Iron Man</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/660142</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr"/>
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>48-55</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr"/>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr"/>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr"/>
+      <c r="L2" s="9" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Donkey Kong</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Funky Kong</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/549673</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Bluster Kong</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">https://discord.gg/PdTDUgNYaY </t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>64-71</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Open Beta</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
@@ -755,50 +4015,50 @@
       <c r="L4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Samus</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Mecha Sonic</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/495584</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>80-87</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr"/>
+      <c r="L5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -921,50 +4181,50 @@
       <c r="L9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Pikachu</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Raichu</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/474333</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>slotted ecosystem; slot range not published</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -997,236 +4257,236 @@
       <c r="L11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Ness</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Kamek</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/510382</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Ninten</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/468526</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>64-71</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K12" s="10" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L12" s="10" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Captain Falcon</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Blood Falcon</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/496231</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Phoenix Wright</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/606758</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>24-31</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>112-119</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K13" s="10" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L13" s="10" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Jigglypuff</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Magolor</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/630469</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>A-Bomb</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/665659</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>96-111</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>32-33</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Peach</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Uravity</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>https://lilylavender.github.io/UltimateMovesetCompatibility/moveset/96</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>100-107</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>Open Beta</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -1259,50 +4519,50 @@
       <c r="L16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Bowser</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>King Leno</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/674935</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>24-31</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr"/>
+      <c r="L17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -1365,262 +4625,262 @@
       <c r="L19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Zelda</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Phosphora</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/471696</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>128-135</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Dr. Mario</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Sandbag</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/481498</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Pawn</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/664660</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>64-71</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>41-48</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K21" s="10" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L21" s="10" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Pichu</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Goomba</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/639737</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L22" s="6" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Falco</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Peppy</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/38894</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr"/>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L23" s="6" t="inlineStr"/>
+      <c r="L23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Marth</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Tetrimino</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/626305</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Goku</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>https://lilylavender.github.io/UltimateMovesetCompatibility/moveset/95</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>20-27</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>80-87</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>Open Beta</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K24" s="10" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L24" s="10" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
@@ -1687,124 +4947,124 @@
       <c r="L26" s="14" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Ganondorf</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Springtrap</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/675046</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Ultron</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/681333</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>16-23</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>64-71</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Open Beta</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K27" s="10" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L27" s="10" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Mewtwo</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Herobrine</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/559266</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Shadow Mewtwo</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/583298</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>32-39</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>24-31</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Pending Update</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K28" s="10" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L28" s="10" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
@@ -1841,50 +5101,50 @@
       <c r="L29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Chrom</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Ichiban</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/660071</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr"/>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>95-103</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="6" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr"/>
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K30" s="6" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L30" s="6" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -1917,50 +5177,50 @@
       <c r="L31" s="14" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Meta Knight</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Dark Meta Knight</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>https://discord.gg/mXGbCkakR</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr"/>
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>72-79</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Open Beta</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr"/>
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L32" s="6" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -1993,62 +5253,62 @@
       <c r="L33" s="14" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Dark Pit</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Krystal</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/514829</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Decidueye</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/513821</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>64-71</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>compatible stack; confirm slots on install</t>
         </is>
       </c>
-      <c r="K34" s="10" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L34" s="10" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>slotted ecosystem; slot range not published</t>
         </is>
@@ -2145,62 +5405,62 @@
       <c r="L37" s="14" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Ike</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Monster Hunter</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/678083</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Black Knight</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/589645</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>104-111</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K38" s="10" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L38" s="10" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
@@ -2267,108 +5527,108 @@
       <c r="L40" s="14" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Lucas</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Masked Man</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/489945</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="6" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K41" s="6" t="inlineStr">
+      <c r="K41" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L41" s="6" t="inlineStr"/>
+      <c r="L41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sonic</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Tails</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/635053</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Knuckles</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/606587</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>64-71</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J42" s="10" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L42" s="10" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
@@ -2405,96 +5665,96 @@
       <c r="L43" s="14" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Olimar</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Rayman</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/38894</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr"/>
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="6" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr"/>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr"/>
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K44" s="6" t="inlineStr">
+      <c r="K44" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L44" s="6" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Lucario</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Vegeta</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/469216</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="6" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr"/>
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K45" s="6" t="inlineStr">
+      <c r="K45" s="9" t="inlineStr">
         <is>
           <t>slotted ecosystem; slot range not published</t>
         </is>
       </c>
-      <c r="L45" s="6" t="inlineStr"/>
+      <c r="L45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -2557,154 +5817,154 @@
       <c r="L47" s="14" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>Wolf</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Zeraora</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/524527</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr"/>
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="6" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K48" s="6" t="inlineStr">
+      <c r="K48" s="9" t="inlineStr">
         <is>
           <t>slotted ecosystem; slot range not published</t>
         </is>
       </c>
-      <c r="L48" s="6" t="inlineStr"/>
+      <c r="L48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Villager</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Toad</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/38894</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr"/>
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="6" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr">
+      <c r="K49" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L49" s="6" t="inlineStr"/>
+      <c r="L49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Mega Man</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/605585</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Colette</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/561040</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>95-102</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J50" s="10" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>compatible stack; confirm slots on install</t>
         </is>
       </c>
-      <c r="K50" s="10" t="inlineStr">
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L50" s="10" t="inlineStr">
+      <c r="L50" s="5" t="inlineStr">
         <is>
           <t>slotted ecosystem; slot range not published</t>
         </is>
@@ -2771,96 +6031,96 @@
       <c r="L52" s="14" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Little Mac</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Naruto Uzumaki</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/478432</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr"/>
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="6" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr"/>
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K53" s="6" t="inlineStr">
+      <c r="K53" s="9" t="inlineStr">
         <is>
           <t>slotted ecosystem; slot range not published</t>
         </is>
       </c>
-      <c r="L53" s="6" t="inlineStr"/>
+      <c r="L53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Greninja</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Chaos</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/641872</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr"/>
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>64-71</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr"/>
-      <c r="J54" s="6" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr"/>
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K54" s="6" t="inlineStr">
+      <c r="K54" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L54" s="6" t="inlineStr"/>
+      <c r="L54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -2953,158 +6213,158 @@
       <c r="L57" s="14" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Palutena</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Sans</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/549674</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Sailor Moon</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/390285</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>128-135</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J58" s="10" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K58" s="10" t="inlineStr">
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L58" s="10" t="inlineStr">
+      <c r="L58" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>PAC-Man</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Bomberman</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/38894</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr"/>
-      <c r="J59" s="6" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K59" s="6" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L59" s="6" t="inlineStr"/>
+      <c r="L59" s="9" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Robin</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Mona</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/533215</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr"/>
-      <c r="J60" s="6" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K60" s="6" t="inlineStr">
+      <c r="K60" s="9" t="inlineStr">
         <is>
           <t>slotted ecosystem; slot range not published</t>
         </is>
       </c>
-      <c r="L60" s="6" t="inlineStr"/>
+      <c r="L60" s="9" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -3227,50 +6487,50 @@
       <c r="L64" s="14" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>Ken</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Vegeta</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/699357</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr"/>
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>95-102</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr"/>
-      <c r="J65" s="6" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K65" s="6" t="inlineStr">
+      <c r="K65" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L65" s="6" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
@@ -3303,50 +6563,50 @@
       <c r="L66" s="14" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>Corrin</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Potemkin</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>https://lilylavender.github.io/UltimateMovesetCompatibility/moveset/45</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>128-144</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr"/>
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>Open Beta</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="6" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K67" s="6" t="inlineStr">
+      <c r="K67" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L67" s="6" t="inlineStr"/>
+      <c r="L67" s="9" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -3469,50 +6729,50 @@
       <c r="L71" s="14" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Richter</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>Alucard</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/457661</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr"/>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr"/>
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr"/>
-      <c r="J72" s="6" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr"/>
+      <c r="J72" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K72" s="6" t="inlineStr">
+      <c r="K72" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L72" s="6" t="inlineStr"/>
+      <c r="L72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -3665,154 +6925,154 @@
       <c r="L77" s="14" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>Hero</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>Megumin</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/660152</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr"/>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr"/>
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>64-71</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr"/>
-      <c r="J78" s="6" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K78" s="6" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L78" s="6" t="inlineStr"/>
+      <c r="L78" s="9" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Banjo &amp; Kazooie</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>Cuphead</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/633920</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr"/>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>32-39</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr"/>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr"/>
-      <c r="J79" s="6" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K79" s="6" t="inlineStr">
+      <c r="K79" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L79" s="6" t="inlineStr"/>
+      <c r="L79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="7" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Terry</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Waluigi</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/443150</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Meiling</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/583913</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>70-79</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="J80" s="10" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>verified conflict-free</t>
         </is>
       </c>
-      <c r="K80" s="10" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L80" s="10" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
@@ -3909,50 +7169,50 @@
       <c r="L83" s="14" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>Sephiroth</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>Bandana Dee</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>https://gamebanana.com/mods/580288</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>NONE AVAILABLE</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr"/>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>NONE AVAILABLE</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr"/>
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>120-127</t>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr"/>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr"/>
-      <c r="J84" s="6" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr"/>
+      <c r="J84" s="9" t="inlineStr">
         <is>
           <t>single option available</t>
         </is>
       </c>
-      <c r="K84" s="6" t="inlineStr">
+      <c r="K84" s="9" t="inlineStr">
         <is>
           <t>verified (slots+hooks checked)</t>
         </is>
       </c>
-      <c r="L84" s="6" t="inlineStr"/>
+      <c r="L84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
@@ -4105,318 +7365,404 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="118" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>Setup &amp; Compatibility Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>REQUIRED PLUGIN STACK (install once, before adding any moveset)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Dependency</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>Download</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>The CSK Collection</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>https://gamebanana.com/mods/499008</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>NRO Hook</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>https://github.com/ultimate-research/nro-hook-plugin/releases</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Smashline 2</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>https://github.com/HDR-Development/smashline</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>ARCropolis</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>https://github.com/Raytwo/ARCropolis</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Skyline</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>https://github.com/skyline-dev/skyline</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>paramconfig</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>https://github.com/CSharpM7/lib_paramconfig</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>One Slot Effects</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>https://gamebanana.com/mods/549058</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>CONFIDENCE LEVELS (see sugg1_confidence / sugg2_confidence)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>'verified (slots+hooks checked)' - tracked in the Ultimate Moveset Compatibility database. Costume slot range and</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    hooked memory offsets are published, so conflicts were checked programmatically. Highest confidence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>'slotted ecosystem; slot range not published' - GameBanana mod confirmed to use the CSK slotting method / Smashline 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (same plugin stack), but its slot range is not published, so overlap could not be auto-verified. Confirm on install.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>WHY THESE MODS ARE INTERCOMPATIBLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>1. Every listed moveset is SLOTTED: it occupies specific costume slots rather than replacing the fighter globally,</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    so several can coexist. Two movesets on one fighter are fine as long as their slot ranges differ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>2. All share the Smashline 2 + ARCropolis + CSK stack above - one plugin set, not competing ones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>3. Tier-A pairs were checked for slot-range overlap, shared hooked memory offsets, and concurrent global 'opff' hooks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>4. EXCLUDED: non-slotted movesets, which overwrite the whole fighter and break every other mod on it. The most popular</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    moveset in the game (Shadow the Hedgehog, 465 likes) is excluded for exactly this reason - it states no slotting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>5. Also excluded: reworks of a vanilla fighter (Sonic Re-Imagined, Dread Samus, Swole Luigi). They change the original</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    character rather than replacing them, so they do not answer 'which mod character replaces X'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>6. Slot ranges can be reassigned with a reslotter tool if you hit an overlap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>7. Movesets are NOT Wi-Fi safe - offline / local play only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>COVERAGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>39 of 86 fighters have at least one custom moveset; 14 have two. 47 have none in existence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>'NONE AVAILABLE' means no such mod has been made - not that it was omitted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>Roster = 86 in-game fighter slots (Pokemon Trainer = 1 entry, Pyra / Mythra = 1 entry).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>https://lilylavender.github.io/UltimateMovesetCompatibility/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>https://gamebanana.com/mods/cats/3325</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId9"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="118" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Setup &amp; Compatibility Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>BUILDING AN ALL-MOD ROSTER (no vanilla characters visible)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Yes - this works, and a prebuilt CSS already does it. Two things make it possible:</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A) Each slotted moveset gets its OWN character-select icon, not a costume of its host. The CSK Collection API</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     can 'Add Entries to the Character Database / Character Layout Database', so Tails and Knuckles both sitting on</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Sonic still appear as two separate roster entries. That is the normal behaviour, not a workaround.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B) Vanilla fighters are HIDDEN, not deleted. A slotted moveset runs on its host fighter, so the host must still exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     internally. You remove its CSS entry so it is not selectable. CoolSonicKirby's CSS Manager exposes every</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     modded character in a hidden section and lets you place/hide slots freely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Prebuilt option - 'Oops, All Character Mods!' : an all-mod CSS with no base roster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    55 modded characters on the main CSS + 36 on an alt CSS (94 total).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    https://gamebanana.com/mods/638920</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Required alongside it: Ultimate CSS 91+ Layout Fix (raises the 91-slot cap; 170 now, 255 is the hard cap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    https://gamebanana.com/mods/573626</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>HARD LIMITS AND WARNINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- Memory, not slot count, is the real ceiling: ~55 modded characters per CSS. Loading more (including any base</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    roster characters) causes a permanent load when starting a match. Dropping the vanilla roster is what buys the room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>- 255 CSS slots is the layout cap, but you will hit the memory wall long before that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>- Load times can reach ~10 minutes with a full modded roster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>- The all-mod CSS above is reported as tested on EMULATOR only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>- Missing mods just leave blank slots - harmless. But picking RANDOM with an unslotted character will freeze the game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>- Movesets are NOT Wi-Fi safe. Offline / local play only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>REQUIRED PLUGIN STACK (install once)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>The CSK Collection</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/499008</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NRO Hook</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/ultimate-research/nro-hook-plugin/releases</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Smashline 2</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/HDR-Development/smashline</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ARCropolis</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/Raytwo/ARCropolis</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Skyline</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/skyline-dev/skyline</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>paramconfig</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>https://github.com/CSharpM7/lib_paramconfig</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>One Slot Effects</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/549058</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>CONFLICT STATUS OF THIS ROSTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>All 72 mod characters were checked for costume slot-range overlap on their shared host fighters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Result: 0 conflicts among the 59 with published slot ranges - the whole roster can be loaded together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>13 mods do not publish a slot range (shaded yellow); confirm those on install, or reslot them if they collide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Slot ranges can be reassigned with a reslotter tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>EXCLUDED ON PURPOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>- Non-slotted movesets, which take over a fighter globally and break other mods on it. This is why Shadow the</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Hedgehog (the game's most-liked moveset, 465 likes) is not here - its page states no slotting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>- Reworks of vanilla fighters (Sonic Re-Imagined, Dread Samus, Swole Luigi): they alter the original character</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rather than replacing them, so they do not belong on an all-mod roster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>https://lilylavender.github.io/UltimateMovesetCompatibility/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>https://gamebanana.com/mods/cats/3325</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId11"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4424,70 +7770,101 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>Fighters on roster</t>
-        </is>
-      </c>
-      <c r="B2" s="21">
-        <f>COUNTA('Moveset Mods'!A2:A87)</f>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Playable mod characters available</t>
+        </is>
+      </c>
+      <c r="B2" s="20">
+        <f>COUNTA('Mod Roster'!A2:A73)</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>With published slot range (verified)</t>
+        </is>
+      </c>
+      <c r="B3" s="20">
+        <f>COUNTIF('Mod Roster'!D2:D73,"&lt;&gt;not published")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Needing manual slot check</t>
+        </is>
+      </c>
+      <c r="B4" s="20">
+        <f>COUNTIF('Mod Roster'!D2:D73,"not published")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Host fighters used</t>
+        </is>
+      </c>
+      <c r="B5" s="20">
+        <f>SUMPRODUCT(1/COUNTIF('Mod Roster'!C2:C73,'Mod Roster'!C2:C73))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Fighters with at least 1 moveset</t>
         </is>
       </c>
-      <c r="B3" s="21">
-        <f>COUNTIF('Moveset Mods'!B2:B87,"&lt;&gt;NONE AVAILABLE")</f>
+      <c r="B6" s="20">
+        <f>COUNTIF('By Original Char'!B2:B87,"&lt;&gt;NONE AVAILABLE")</f>
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>Fighters with 2 suggestions</t>
-        </is>
-      </c>
-      <c r="B4" s="21">
-        <f>COUNTIF('Moveset Mods'!D2:D87,"&lt;&gt;NONE AVAILABLE")</f>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Fighters with NO moveset</t>
+        </is>
+      </c>
+      <c r="B7" s="20">
+        <f>COUNTIF('By Original Char'!B2:B87,"NONE AVAILABLE")</f>
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>Fighters with NO moveset</t>
-        </is>
-      </c>
-      <c r="B5" s="21">
-        <f>COUNTIF('Moveset Mods'!B2:B87,"NONE AVAILABLE")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Pairs verified conflict-free</t>
-        </is>
-      </c>
-      <c r="B6" s="21">
-        <f>COUNTIF('Moveset Mods'!J2:J87,"verified conflict-free")</f>
-        <v/>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Max mods per CSS (memory limit)</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>CSS slot hard cap</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
